--- a/Roguelike/Assets/ScriptableObject/Armors/Armors.xlsx
+++ b/Roguelike/Assets/ScriptableObject/Armors/Armors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hosokawashigeki/Documents/Unity/Roguelike/Assets/ScriptableObject/Armors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C0924A-B53F-8A44-B590-521B0E2CE469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B820F2DB-1B15-704A-A69A-F4B544CB4FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14820" yWindow="500" windowWidth="13980" windowHeight="17500" xr2:uid="{6F905B51-AFFA-5F45-B83A-891FE383EE9A}"/>
   </bookViews>
@@ -598,7 +598,7 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>4500</v>
@@ -618,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>12600</v>
